--- a/artfynd/A 55383-2022 artfynd.xlsx
+++ b/artfynd/A 55383-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55383-2022 artfynd.xlsx
+++ b/artfynd/A 55383-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AY80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8849,6 +8849,448 @@
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>121648924</v>
+      </c>
+      <c r="B77" t="n">
+        <v>90738</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Svarthån, Hjd</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>409498</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6940878</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>121648923</v>
+      </c>
+      <c r="B78" t="n">
+        <v>91066</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>2063</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Grantickeporing</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Skeletocutis chrysella</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Svarthån, Hjd</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>409528</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6940887</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>121648920</v>
+      </c>
+      <c r="B79" t="n">
+        <v>91653</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Rönningsåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>409607</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6941437</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>121648919</v>
+      </c>
+      <c r="B80" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Rönningsåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>409581</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6941403</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55383-2022 artfynd.xlsx
+++ b/artfynd/A 55383-2022 artfynd.xlsx
@@ -8851,10 +8851,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121648924</v>
+        <v>121648919</v>
       </c>
       <c r="B77" t="n">
-        <v>90738</v>
+        <v>78616</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8867,34 +8867,43 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Svarthån, Hjd</t>
+          <t>Rönningsåsen, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>409498</v>
+        <v>409581</v>
       </c>
       <c r="R77" t="n">
-        <v>6940878</v>
+        <v>6941403</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8960,7 +8969,7 @@
         <v>121648923</v>
       </c>
       <c r="B78" t="n">
-        <v>91066</v>
+        <v>91074</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9066,7 +9075,7 @@
         <v>121648920</v>
       </c>
       <c r="B79" t="n">
-        <v>91653</v>
+        <v>91661</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9178,10 +9187,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121648919</v>
+        <v>121648924</v>
       </c>
       <c r="B80" t="n">
-        <v>78609</v>
+        <v>90746</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9194,43 +9203,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Rönningsåsen, Hjd</t>
+          <t>Svarthån, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409581</v>
+        <v>409498</v>
       </c>
       <c r="R80" t="n">
-        <v>6941403</v>
+        <v>6940878</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 55383-2022 artfynd.xlsx
+++ b/artfynd/A 55383-2022 artfynd.xlsx
@@ -8851,10 +8851,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121648919</v>
+        <v>121648923</v>
       </c>
       <c r="B77" t="n">
-        <v>78616</v>
+        <v>91074</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8863,47 +8863,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>2063</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Rönningsåsen, Hjd</t>
+          <t>Svarthån, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>409581</v>
+        <v>409528</v>
       </c>
       <c r="R77" t="n">
-        <v>6941403</v>
+        <v>6940887</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8966,10 +8957,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121648923</v>
+        <v>121648919</v>
       </c>
       <c r="B78" t="n">
-        <v>91074</v>
+        <v>78616</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8978,38 +8969,47 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2063</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Svarthån, Hjd</t>
+          <t>Rönningsåsen, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>409528</v>
+        <v>409581</v>
       </c>
       <c r="R78" t="n">
-        <v>6940887</v>
+        <v>6941403</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 55383-2022 artfynd.xlsx
+++ b/artfynd/A 55383-2022 artfynd.xlsx
@@ -8851,10 +8851,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121648920</v>
+        <v>121648924</v>
       </c>
       <c r="B77" t="n">
-        <v>91661</v>
+        <v>90746</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8863,47 +8863,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Rönningsåsen, Hjd</t>
+          <t>Svarthån, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>409607</v>
+        <v>409498</v>
       </c>
       <c r="R77" t="n">
-        <v>6941437</v>
+        <v>6940878</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8966,10 +8957,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121648924</v>
+        <v>121648923</v>
       </c>
       <c r="B78" t="n">
-        <v>90746</v>
+        <v>91074</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8978,25 +8969,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5432</v>
+        <v>2063</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9006,10 +8997,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>409498</v>
+        <v>409528</v>
       </c>
       <c r="R78" t="n">
-        <v>6940878</v>
+        <v>6940887</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9072,10 +9063,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121648923</v>
+        <v>121648920</v>
       </c>
       <c r="B79" t="n">
-        <v>91074</v>
+        <v>91661</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9084,38 +9075,47 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2063</v>
+        <v>4769</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Svarthån, Hjd</t>
+          <t>Rönningsåsen, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>409528</v>
+        <v>409607</v>
       </c>
       <c r="R79" t="n">
-        <v>6940887</v>
+        <v>6941437</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>

--- a/artfynd/A 55383-2022 artfynd.xlsx
+++ b/artfynd/A 55383-2022 artfynd.xlsx
@@ -8851,10 +8851,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121648924</v>
+        <v>121648920</v>
       </c>
       <c r="B77" t="n">
-        <v>90746</v>
+        <v>91661</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8863,38 +8863,47 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Svarthån, Hjd</t>
+          <t>Rönningsåsen, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>409498</v>
+        <v>409607</v>
       </c>
       <c r="R77" t="n">
-        <v>6940878</v>
+        <v>6941437</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9063,10 +9072,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121648920</v>
+        <v>121648919</v>
       </c>
       <c r="B79" t="n">
-        <v>91661</v>
+        <v>78616</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9075,35 +9084,35 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9112,10 +9121,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>409607</v>
+        <v>409581</v>
       </c>
       <c r="R79" t="n">
-        <v>6941437</v>
+        <v>6941403</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9178,10 +9187,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121648919</v>
+        <v>121648924</v>
       </c>
       <c r="B80" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9194,43 +9203,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Rönningsåsen, Hjd</t>
+          <t>Svarthån, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409581</v>
+        <v>409498</v>
       </c>
       <c r="R80" t="n">
-        <v>6941403</v>
+        <v>6940878</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 55383-2022 artfynd.xlsx
+++ b/artfynd/A 55383-2022 artfynd.xlsx
@@ -8851,10 +8851,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121648920</v>
+        <v>121648923</v>
       </c>
       <c r="B77" t="n">
-        <v>91661</v>
+        <v>91074</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8863,47 +8863,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4769</v>
+        <v>2063</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Rönningsåsen, Hjd</t>
+          <t>Svarthån, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>409607</v>
+        <v>409528</v>
       </c>
       <c r="R77" t="n">
-        <v>6941437</v>
+        <v>6940887</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8966,10 +8957,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121648923</v>
+        <v>121648920</v>
       </c>
       <c r="B78" t="n">
-        <v>91074</v>
+        <v>91661</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8978,38 +8969,47 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2063</v>
+        <v>4769</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Svarthån, Hjd</t>
+          <t>Rönningsåsen, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>409528</v>
+        <v>409607</v>
       </c>
       <c r="R78" t="n">
-        <v>6940887</v>
+        <v>6941437</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 55383-2022 artfynd.xlsx
+++ b/artfynd/A 55383-2022 artfynd.xlsx
@@ -8957,10 +8957,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121648920</v>
+        <v>121648924</v>
       </c>
       <c r="B78" t="n">
-        <v>91661</v>
+        <v>90746</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8969,47 +8969,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Rönningsåsen, Hjd</t>
+          <t>Svarthån, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>409607</v>
+        <v>409498</v>
       </c>
       <c r="R78" t="n">
-        <v>6941437</v>
+        <v>6940878</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9187,10 +9178,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121648924</v>
+        <v>121648920</v>
       </c>
       <c r="B80" t="n">
-        <v>90746</v>
+        <v>91661</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9199,38 +9190,47 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Svarthån, Hjd</t>
+          <t>Rönningsåsen, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409498</v>
+        <v>409607</v>
       </c>
       <c r="R80" t="n">
-        <v>6940878</v>
+        <v>6941437</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 55383-2022 artfynd.xlsx
+++ b/artfynd/A 55383-2022 artfynd.xlsx
@@ -8851,10 +8851,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121648923</v>
+        <v>121648924</v>
       </c>
       <c r="B77" t="n">
-        <v>91074</v>
+        <v>90746</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8863,25 +8863,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2063</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>409528</v>
+        <v>409498</v>
       </c>
       <c r="R77" t="n">
-        <v>6940887</v>
+        <v>6940878</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8957,10 +8957,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121648924</v>
+        <v>121648923</v>
       </c>
       <c r="B78" t="n">
-        <v>90746</v>
+        <v>91074</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8969,25 +8969,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5432</v>
+        <v>2063</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8997,10 +8997,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>409498</v>
+        <v>409528</v>
       </c>
       <c r="R78" t="n">
-        <v>6940878</v>
+        <v>6940887</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9063,10 +9063,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121648919</v>
+        <v>121648920</v>
       </c>
       <c r="B79" t="n">
-        <v>78616</v>
+        <v>91661</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9075,35 +9075,35 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9112,10 +9112,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>409581</v>
+        <v>409607</v>
       </c>
       <c r="R79" t="n">
-        <v>6941403</v>
+        <v>6941437</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9178,10 +9178,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121648920</v>
+        <v>121648919</v>
       </c>
       <c r="B80" t="n">
-        <v>91661</v>
+        <v>78616</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9190,35 +9190,35 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9227,10 +9227,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409607</v>
+        <v>409581</v>
       </c>
       <c r="R80" t="n">
-        <v>6941437</v>
+        <v>6941403</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 55383-2022 artfynd.xlsx
+++ b/artfynd/A 55383-2022 artfynd.xlsx
@@ -8851,10 +8851,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121648920</v>
+        <v>121648923</v>
       </c>
       <c r="B77" t="n">
-        <v>91661</v>
+        <v>91088</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8863,47 +8863,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4769</v>
+        <v>2063</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Rönningsåsen, Hjd</t>
+          <t>Svarthån, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>409607</v>
+        <v>409528</v>
       </c>
       <c r="R77" t="n">
-        <v>6941437</v>
+        <v>6940887</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8966,10 +8957,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121648923</v>
+        <v>121648919</v>
       </c>
       <c r="B78" t="n">
-        <v>91074</v>
+        <v>78629</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8978,38 +8969,47 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2063</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Svarthån, Hjd</t>
+          <t>Rönningsåsen, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>409528</v>
+        <v>409581</v>
       </c>
       <c r="R78" t="n">
-        <v>6940887</v>
+        <v>6941403</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9072,10 +9072,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121648919</v>
+        <v>121648924</v>
       </c>
       <c r="B79" t="n">
-        <v>78616</v>
+        <v>90760</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9088,43 +9088,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Rönningsåsen, Hjd</t>
+          <t>Svarthån, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>409581</v>
+        <v>409498</v>
       </c>
       <c r="R79" t="n">
-        <v>6941403</v>
+        <v>6940878</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9187,10 +9178,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121648924</v>
+        <v>121648920</v>
       </c>
       <c r="B80" t="n">
-        <v>90746</v>
+        <v>91675</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9199,38 +9190,47 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Svarthån, Hjd</t>
+          <t>Rönningsåsen, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409498</v>
+        <v>409607</v>
       </c>
       <c r="R80" t="n">
-        <v>6940878</v>
+        <v>6941437</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 55383-2022 artfynd.xlsx
+++ b/artfynd/A 55383-2022 artfynd.xlsx
@@ -8854,7 +8854,7 @@
         <v>121648923</v>
       </c>
       <c r="B77" t="n">
-        <v>91088</v>
+        <v>91090</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>121648919</v>
       </c>
       <c r="B78" t="n">
-        <v>78629</v>
+        <v>78631</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9072,10 +9072,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121648924</v>
+        <v>121648920</v>
       </c>
       <c r="B79" t="n">
-        <v>90760</v>
+        <v>91677</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9084,38 +9084,47 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Svarthån, Hjd</t>
+          <t>Rönningsåsen, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>409498</v>
+        <v>409607</v>
       </c>
       <c r="R79" t="n">
-        <v>6940878</v>
+        <v>6941437</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9178,10 +9187,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121648920</v>
+        <v>121648924</v>
       </c>
       <c r="B80" t="n">
-        <v>91675</v>
+        <v>90762</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9190,47 +9199,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Rönningsåsen, Hjd</t>
+          <t>Svarthån, Hjd</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409607</v>
+        <v>409498</v>
       </c>
       <c r="R80" t="n">
-        <v>6941437</v>
+        <v>6940878</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 55383-2022 artfynd.xlsx
+++ b/artfynd/A 55383-2022 artfynd.xlsx
@@ -8851,10 +8851,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121648923</v>
+        <v>121648919</v>
       </c>
       <c r="B77" t="n">
-        <v>91090</v>
+        <v>78632</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8863,38 +8863,47 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2063</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Svarthån, Hjd</t>
+          <t>Rönningsåsen, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>409528</v>
+        <v>409581</v>
       </c>
       <c r="R77" t="n">
-        <v>6940887</v>
+        <v>6941403</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8957,10 +8966,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121648919</v>
+        <v>121648920</v>
       </c>
       <c r="B78" t="n">
-        <v>78631</v>
+        <v>91678</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8969,35 +8978,35 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9006,10 +9015,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>409581</v>
+        <v>409607</v>
       </c>
       <c r="R78" t="n">
-        <v>6941403</v>
+        <v>6941437</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9072,10 +9081,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121648920</v>
+        <v>121648923</v>
       </c>
       <c r="B79" t="n">
-        <v>91677</v>
+        <v>91091</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9084,47 +9093,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4769</v>
+        <v>2063</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Rönningsåsen, Hjd</t>
+          <t>Svarthån, Hjd</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>409607</v>
+        <v>409528</v>
       </c>
       <c r="R79" t="n">
-        <v>6941437</v>
+        <v>6940887</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9190,7 +9190,7 @@
         <v>121648924</v>
       </c>
       <c r="B80" t="n">
-        <v>90762</v>
+        <v>90763</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>

--- a/artfynd/A 55383-2022 artfynd.xlsx
+++ b/artfynd/A 55383-2022 artfynd.xlsx
@@ -2077,7 +2077,7 @@
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="b">
         <v>0</v>
@@ -4158,7 +4158,7 @@
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG33" t="b">
         <v>0</v>
@@ -6230,7 +6230,7 @@
         <v>0</v>
       </c>
       <c r="AE52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG52" t="b">
         <v>0</v>

--- a/artfynd/A 55383-2022 artfynd.xlsx
+++ b/artfynd/A 55383-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY80"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112619959</v>
+        <v>121648923</v>
       </c>
       <c r="B2" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92283</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>rönningsåsen s., Hjd</t>
+          <t>Svarthån, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409578</v>
+        <v>409528</v>
       </c>
       <c r="R2" t="n">
-        <v>6941229</v>
+        <v>6940887</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-09</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,66 +760,61 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112619990</v>
+        <v>112620059</v>
       </c>
       <c r="B3" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>rönningsåsen s., Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409390</v>
+        <v>409384</v>
       </c>
       <c r="R3" t="n">
-        <v>6941082</v>
+        <v>6941086</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,11 +847,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-10-09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,15 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112619979</v>
+        <v>112619950</v>
       </c>
       <c r="B4" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,21 +901,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>rönningsåsen s., Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409522</v>
+        <v>409414</v>
       </c>
       <c r="R4" t="n">
-        <v>6941082</v>
+        <v>6941097</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-10-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,15 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112620042</v>
+        <v>112619956</v>
       </c>
       <c r="B5" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,34 +997,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>rönningsåsen s., Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409510</v>
+        <v>409520</v>
       </c>
       <c r="R5" t="n">
-        <v>6941155</v>
+        <v>6941295</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,6 +1061,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-10-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,15 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112620031</v>
+        <v>112619957</v>
       </c>
       <c r="B6" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,34 +1103,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>rönningsåsen s., Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>409590</v>
+        <v>409538</v>
       </c>
       <c r="R6" t="n">
-        <v>6941456</v>
+        <v>6941269</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,6 +1167,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-10-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1212,15 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112619961</v>
+        <v>112619958</v>
       </c>
       <c r="B7" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409574</v>
+        <v>409543</v>
       </c>
       <c r="R7" t="n">
-        <v>6941168</v>
+        <v>6941228</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,7 +1277,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,15 +1304,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112620013</v>
+        <v>112619965</v>
       </c>
       <c r="B8" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>409536</v>
+        <v>409492</v>
       </c>
       <c r="R8" t="n">
-        <v>6940970</v>
+        <v>6941269</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1383,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,15 +1410,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112619996</v>
+        <v>112619966</v>
       </c>
       <c r="B9" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,7 +1441,11 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1478,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>409427</v>
+        <v>409334</v>
       </c>
       <c r="R9" t="n">
-        <v>6940907</v>
+        <v>6941277</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,16 +1491,11 @@
           <t>2023-10-09</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
@@ -1545,15 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112619950</v>
+        <v>112619967</v>
       </c>
       <c r="B10" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,33 +1543,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>rönningsåsen s., Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>409414</v>
+        <v>409336</v>
       </c>
       <c r="R10" t="n">
-        <v>6941097</v>
+        <v>6941262</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,6 +1590,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-10-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,15 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112620047</v>
+        <v>112619968</v>
       </c>
       <c r="B11" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1679,34 +1632,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>rönningsåsen s., Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>409458</v>
+        <v>409348</v>
       </c>
       <c r="R11" t="n">
-        <v>6940919</v>
+        <v>6941250</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,6 +1696,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-10-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,15 +1727,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112620009</v>
+        <v>112619969</v>
       </c>
       <c r="B12" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,10 +1766,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>409510</v>
+        <v>409368</v>
       </c>
       <c r="R12" t="n">
-        <v>6940975</v>
+        <v>6941239</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1876,15 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112620006</v>
+        <v>112619970</v>
       </c>
       <c r="B13" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1920,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>409540</v>
+        <v>409367</v>
       </c>
       <c r="R13" t="n">
-        <v>6940867</v>
+        <v>6941264</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1960,7 +1912,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,15 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112619998</v>
+        <v>112619972</v>
       </c>
       <c r="B14" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,11 +1970,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2035,10 +1978,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>409458</v>
+        <v>409443</v>
       </c>
       <c r="R14" t="n">
-        <v>6940919</v>
+        <v>6941284</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,11 +2016,16 @@
           <t>2023-10-09</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="b">
         <v>0</v>
@@ -2097,15 +2045,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112620001</v>
+        <v>112619973</v>
       </c>
       <c r="B15" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2141,10 +2084,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>409484</v>
+        <v>409443</v>
       </c>
       <c r="R15" t="n">
-        <v>6940902</v>
+        <v>6941247</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2181,7 +2124,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2208,15 +2151,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112619973</v>
+        <v>112619974</v>
       </c>
       <c r="B16" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,10 +2190,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>409443</v>
+        <v>409442</v>
       </c>
       <c r="R16" t="n">
-        <v>6941247</v>
+        <v>6941210</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2319,15 +2257,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112620018</v>
+        <v>112619976</v>
       </c>
       <c r="B17" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2363,10 +2296,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>409544</v>
+        <v>409448</v>
       </c>
       <c r="R17" t="n">
-        <v>6941010</v>
+        <v>6941217</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2403,7 +2336,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2430,15 +2363,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112620016</v>
+        <v>112619977</v>
       </c>
       <c r="B18" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2474,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>409542</v>
+        <v>409524</v>
       </c>
       <c r="R18" t="n">
-        <v>6940999</v>
+        <v>6941109</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2514,7 +2442,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2541,15 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112619987</v>
+        <v>112619978</v>
       </c>
       <c r="B19" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,10 +2508,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>409340</v>
+        <v>409524</v>
       </c>
       <c r="R19" t="n">
-        <v>6941168</v>
+        <v>6941094</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2652,15 +2575,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112619963</v>
+        <v>112619979</v>
       </c>
       <c r="B20" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,10 +2614,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>409546</v>
+        <v>409522</v>
       </c>
       <c r="R20" t="n">
-        <v>6941091</v>
+        <v>6941081</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2736,7 +2654,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2763,15 +2681,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112619986</v>
+        <v>112619980</v>
       </c>
       <c r="B21" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2807,10 +2720,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>409352</v>
+        <v>409502</v>
       </c>
       <c r="R21" t="n">
-        <v>6941172</v>
+        <v>6941068</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2874,15 +2787,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112620004</v>
+        <v>112619981</v>
       </c>
       <c r="B22" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2918,10 +2826,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>409519</v>
+        <v>409474</v>
       </c>
       <c r="R22" t="n">
-        <v>6940888</v>
+        <v>6940983</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2958,7 +2866,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2985,15 +2893,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112620010</v>
+        <v>112619982</v>
       </c>
       <c r="B23" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3029,10 +2932,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>409513</v>
+        <v>409479</v>
       </c>
       <c r="R23" t="n">
-        <v>6940967</v>
+        <v>6941033</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3069,7 +2972,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3096,15 +2999,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112620052</v>
+        <v>112619983</v>
       </c>
       <c r="B24" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3112,34 +3010,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>rönningsåsen s., Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>409595</v>
+        <v>409425</v>
       </c>
       <c r="R24" t="n">
-        <v>6941226</v>
+        <v>6941099</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3172,6 +3074,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-10-09</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3198,15 +3105,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112619992</v>
+        <v>112619984</v>
       </c>
       <c r="B25" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3242,10 +3144,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409362</v>
+        <v>409427</v>
       </c>
       <c r="R25" t="n">
-        <v>6940895</v>
+        <v>6941119</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3282,7 +3184,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3309,15 +3211,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112620019</v>
+        <v>112619985</v>
       </c>
       <c r="B26" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3353,10 +3250,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409556</v>
+        <v>409424</v>
       </c>
       <c r="R26" t="n">
-        <v>6941011</v>
+        <v>6941121</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3393,7 +3290,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3420,15 +3317,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112620027</v>
+        <v>112619986</v>
       </c>
       <c r="B27" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3464,10 +3356,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>409602</v>
+        <v>409352</v>
       </c>
       <c r="R27" t="n">
-        <v>6941387</v>
+        <v>6941171</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3504,7 +3396,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3531,15 +3423,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112620008</v>
+        <v>112619987</v>
       </c>
       <c r="B28" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3575,10 +3462,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>409529</v>
+        <v>409340</v>
       </c>
       <c r="R28" t="n">
-        <v>6940941</v>
+        <v>6941168</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3642,15 +3529,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112619981</v>
+        <v>112619988</v>
       </c>
       <c r="B29" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3686,10 +3568,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>409474</v>
+        <v>409323</v>
       </c>
       <c r="R29" t="n">
-        <v>6940983</v>
+        <v>6941141</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3726,7 +3608,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3753,15 +3635,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112619983</v>
+        <v>112619989</v>
       </c>
       <c r="B30" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3797,10 +3674,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>409425</v>
+        <v>409373</v>
       </c>
       <c r="R30" t="n">
-        <v>6941099</v>
+        <v>6941108</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3837,7 +3714,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3864,15 +3741,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112620059</v>
+        <v>112619990</v>
       </c>
       <c r="B31" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3880,34 +3752,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>rönningsåsen s., Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>409384</v>
+        <v>409390</v>
       </c>
       <c r="R31" t="n">
-        <v>6941086</v>
+        <v>6941082</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3940,6 +3816,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-10-09</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3966,15 +3847,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112620045</v>
+        <v>112619991</v>
       </c>
       <c r="B32" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3982,34 +3858,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>rönningsåsen s., Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>409349</v>
+        <v>409422</v>
       </c>
       <c r="R32" t="n">
-        <v>6941256</v>
+        <v>6940971</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4042,6 +3922,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-10-09</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4068,15 +3953,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112619966</v>
+        <v>112619992</v>
       </c>
       <c r="B33" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4104,11 +3984,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4116,10 +3992,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>409333</v>
+        <v>409362</v>
       </c>
       <c r="R33" t="n">
-        <v>6941277</v>
+        <v>6940894</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4154,11 +4030,16 @@
           <t>2023-10-09</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="b">
         <v>0</v>
@@ -4178,15 +4059,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112620007</v>
+        <v>112619993</v>
       </c>
       <c r="B34" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4222,10 +4098,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>409544</v>
+        <v>409378</v>
       </c>
       <c r="R34" t="n">
-        <v>6940897</v>
+        <v>6940879</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4262,7 +4138,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4289,15 +4165,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112619991</v>
+        <v>112619994</v>
       </c>
       <c r="B35" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4333,10 +4204,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>409422</v>
+        <v>409414</v>
       </c>
       <c r="R35" t="n">
-        <v>6940971</v>
+        <v>6940866</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4400,15 +4271,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112619977</v>
+        <v>112619995</v>
       </c>
       <c r="B36" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4444,10 +4310,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>409525</v>
+        <v>409428</v>
       </c>
       <c r="R36" t="n">
-        <v>6941110</v>
+        <v>6940885</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4511,15 +4377,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112619988</v>
+        <v>112619996</v>
       </c>
       <c r="B37" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4555,10 +4416,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>409323</v>
+        <v>409427</v>
       </c>
       <c r="R37" t="n">
-        <v>6941141</v>
+        <v>6940907</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4595,7 +4456,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4622,15 +4483,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112620041</v>
+        <v>112619997</v>
       </c>
       <c r="B38" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4638,34 +4494,38 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>rönningsåsen s., Hjd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>409518</v>
+        <v>409440</v>
       </c>
       <c r="R38" t="n">
-        <v>6941149</v>
+        <v>6940901</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4698,6 +4558,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-10-09</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4724,15 +4589,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112620057</v>
+        <v>112619998</v>
       </c>
       <c r="B39" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4740,34 +4600,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>rönningsåsen s., Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>409600</v>
+        <v>409458</v>
       </c>
       <c r="R39" t="n">
-        <v>6941386</v>
+        <v>6940919</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4806,7 +4674,7 @@
         <v>0</v>
       </c>
       <c r="AE39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG39" t="b">
         <v>0</v>
@@ -4826,15 +4694,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112619995</v>
+        <v>112620000</v>
       </c>
       <c r="B40" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4870,10 +4733,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>409428</v>
+        <v>409470</v>
       </c>
       <c r="R40" t="n">
-        <v>6940885</v>
+        <v>6940911</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4910,7 +4773,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4937,15 +4800,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112619962</v>
+        <v>112620001</v>
       </c>
       <c r="B41" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4981,10 +4839,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>409588</v>
+        <v>409484</v>
       </c>
       <c r="R41" t="n">
-        <v>6941116</v>
+        <v>6940902</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5021,7 +4879,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5048,15 +4906,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112619965</v>
+        <v>112620002</v>
       </c>
       <c r="B42" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5092,10 +4945,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>409491</v>
+        <v>409481</v>
       </c>
       <c r="R42" t="n">
-        <v>6941269</v>
+        <v>6940874</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5132,7 +4985,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5159,15 +5012,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112620044</v>
+        <v>112620003</v>
       </c>
       <c r="B43" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5175,34 +5023,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>rönningsåsen s., Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>409404</v>
+        <v>409523</v>
       </c>
       <c r="R43" t="n">
-        <v>6941321</v>
+        <v>6940880</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5235,6 +5087,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-10-09</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5261,15 +5118,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112620043</v>
+        <v>112620004</v>
       </c>
       <c r="B44" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5277,34 +5129,38 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>rönningsåsen s., Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>409515</v>
+        <v>409519</v>
       </c>
       <c r="R44" t="n">
-        <v>6941183</v>
+        <v>6940887</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5337,6 +5193,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-10-09</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5363,15 +5224,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112620020</v>
+        <v>112620005</v>
       </c>
       <c r="B45" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5399,7 +5255,11 @@
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5407,10 +5267,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>409598</v>
+        <v>409523</v>
       </c>
       <c r="R45" t="n">
-        <v>6941114</v>
+        <v>6940888</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5445,16 +5305,11 @@
           <t>2023-10-09</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG45" t="b">
         <v>0</v>
@@ -5474,15 +5329,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112619982</v>
+        <v>112620006</v>
       </c>
       <c r="B46" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5518,10 +5368,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>409479</v>
+        <v>409539</v>
       </c>
       <c r="R46" t="n">
-        <v>6941033</v>
+        <v>6940867</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5585,15 +5435,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112619994</v>
+        <v>112620007</v>
       </c>
       <c r="B47" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5629,10 +5474,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>409414</v>
+        <v>409544</v>
       </c>
       <c r="R47" t="n">
-        <v>6940866</v>
+        <v>6940897</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5669,7 +5514,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5696,15 +5541,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112619993</v>
+        <v>112620008</v>
       </c>
       <c r="B48" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5740,10 +5580,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>409377</v>
+        <v>409528</v>
       </c>
       <c r="R48" t="n">
-        <v>6940879</v>
+        <v>6940941</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5780,7 +5620,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5807,15 +5647,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112620015</v>
+        <v>112620009</v>
       </c>
       <c r="B49" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5851,10 +5686,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>409532</v>
+        <v>409510</v>
       </c>
       <c r="R49" t="n">
-        <v>6940996</v>
+        <v>6940975</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5918,15 +5753,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112620022</v>
+        <v>112620010</v>
       </c>
       <c r="B50" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5962,10 +5792,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>409604</v>
+        <v>409513</v>
       </c>
       <c r="R50" t="n">
-        <v>6941220</v>
+        <v>6940966</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6002,7 +5832,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6029,15 +5859,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112619960</v>
+        <v>112620011</v>
       </c>
       <c r="B51" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6073,10 +5898,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>409567</v>
+        <v>409527</v>
       </c>
       <c r="R51" t="n">
-        <v>6941169</v>
+        <v>6940960</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6113,7 +5938,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6140,15 +5965,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>112620005</v>
+        <v>112620012</v>
       </c>
       <c r="B52" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6176,11 +5996,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6188,10 +6004,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>409524</v>
+        <v>409526</v>
       </c>
       <c r="R52" t="n">
-        <v>6940888</v>
+        <v>6940962</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6226,11 +6042,16 @@
           <t>2023-10-09</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="b">
         <v>0</v>
@@ -6250,15 +6071,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>112620039</v>
+        <v>112620013</v>
       </c>
       <c r="B53" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6266,34 +6082,38 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>rönningsåsen s., Hjd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>409549</v>
+        <v>409536</v>
       </c>
       <c r="R53" t="n">
-        <v>6941069</v>
+        <v>6940970</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6326,6 +6146,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2023-10-09</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6352,15 +6177,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>112620040</v>
+        <v>112620015</v>
       </c>
       <c r="B54" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6368,34 +6188,38 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>rönningsåsen s., Hjd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>409525</v>
+        <v>409532</v>
       </c>
       <c r="R54" t="n">
-        <v>6941141</v>
+        <v>6940996</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6428,6 +6252,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2023-10-09</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6454,15 +6283,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>112620048</v>
+        <v>112620016</v>
       </c>
       <c r="B55" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6470,34 +6294,38 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>rönningsåsen s., Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>409529</v>
+        <v>409542</v>
       </c>
       <c r="R55" t="n">
-        <v>6940885</v>
+        <v>6940999</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6530,6 +6358,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2023-10-09</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6556,15 +6389,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>112620038</v>
+        <v>112620018</v>
       </c>
       <c r="B56" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6572,34 +6400,38 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>rönningsåsen s., Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>409579</v>
+        <v>409544</v>
       </c>
       <c r="R56" t="n">
-        <v>6941111</v>
+        <v>6941010</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6632,6 +6464,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2023-10-09</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6658,54 +6495,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>112619997</v>
+        <v>121648920</v>
       </c>
       <c r="B57" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>rönningsåsen s., Hjd</t>
+          <t>Rönningsåsen, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>409440</v>
+        <v>409607</v>
       </c>
       <c r="R57" t="n">
-        <v>6940900</v>
+        <v>6941437</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6732,17 +6569,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2023-10-09</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2023-10-09</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6757,66 +6589,61 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>112619972</v>
+        <v>112620060</v>
       </c>
       <c r="B58" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>rönningsåsen s., Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>409443</v>
+        <v>409624</v>
       </c>
       <c r="R58" t="n">
-        <v>6941283</v>
+        <v>6941431</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6849,11 +6676,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2023-10-09</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6880,54 +6702,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>112619957</v>
+        <v>121648919</v>
       </c>
       <c r="B59" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>rönningsåsen s., Hjd</t>
+          <t>Rönningsåsen, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>409539</v>
+        <v>409581</v>
       </c>
       <c r="R59" t="n">
-        <v>6941269</v>
+        <v>6941403</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6954,17 +6776,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2023-10-09</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2023-10-09</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6979,27 +6796,26 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>112619964</v>
+        <v>112619959</v>
       </c>
       <c r="B60" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7035,10 +6851,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>409556</v>
+        <v>409578</v>
       </c>
       <c r="R60" t="n">
-        <v>6941099</v>
+        <v>6941229</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7075,7 +6891,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7102,15 +6918,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>112620021</v>
+        <v>112619960</v>
       </c>
       <c r="B61" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7146,10 +6957,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>409613</v>
+        <v>409567</v>
       </c>
       <c r="R61" t="n">
-        <v>6941198</v>
+        <v>6941169</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7213,15 +7024,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>112620011</v>
+        <v>112619961</v>
       </c>
       <c r="B62" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7257,10 +7063,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>409526</v>
+        <v>409574</v>
       </c>
       <c r="R62" t="n">
-        <v>6940960</v>
+        <v>6941168</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7297,7 +7103,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7324,15 +7130,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>112619967</v>
+        <v>112619962</v>
       </c>
       <c r="B63" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7368,10 +7169,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>409336</v>
+        <v>409589</v>
       </c>
       <c r="R63" t="n">
-        <v>6941262</v>
+        <v>6941116</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7408,7 +7209,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7435,15 +7236,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>112620051</v>
+        <v>112619963</v>
       </c>
       <c r="B64" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7451,34 +7247,38 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>rönningsåsen s., Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>409613</v>
+        <v>409546</v>
       </c>
       <c r="R64" t="n">
-        <v>6941198</v>
+        <v>6941091</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7511,6 +7311,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2023-10-09</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7537,15 +7342,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>112620002</v>
+        <v>112619964</v>
       </c>
       <c r="B65" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7581,10 +7381,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>409482</v>
+        <v>409555</v>
       </c>
       <c r="R65" t="n">
-        <v>6940874</v>
+        <v>6941099</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7648,15 +7448,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>112620000</v>
+        <v>112620019</v>
       </c>
       <c r="B66" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7692,10 +7487,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>409470</v>
+        <v>409556</v>
       </c>
       <c r="R66" t="n">
-        <v>6940911</v>
+        <v>6941011</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7732,7 +7527,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7759,15 +7554,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>112620028</v>
+        <v>112620020</v>
       </c>
       <c r="B67" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7803,10 +7593,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>409612</v>
+        <v>409598</v>
       </c>
       <c r="R67" t="n">
-        <v>6941389</v>
+        <v>6941113</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7843,7 +7633,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7870,15 +7660,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>112619968</v>
+        <v>112620021</v>
       </c>
       <c r="B68" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7914,10 +7699,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>409348</v>
+        <v>409613</v>
       </c>
       <c r="R68" t="n">
-        <v>6941250</v>
+        <v>6941197</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7954,7 +7739,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7981,15 +7766,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>112619958</v>
+        <v>112620022</v>
       </c>
       <c r="B69" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8025,10 +7805,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>409543</v>
+        <v>409604</v>
       </c>
       <c r="R69" t="n">
-        <v>6941228</v>
+        <v>6941221</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8065,7 +7845,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8092,15 +7872,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>112620035</v>
+        <v>112620024</v>
       </c>
       <c r="B70" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8108,34 +7883,38 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>rönningsåsen s., Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>409548</v>
+        <v>409629</v>
       </c>
       <c r="R70" t="n">
-        <v>6941252</v>
+        <v>6941245</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8168,6 +7947,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2023-10-09</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8194,15 +7978,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>112620037</v>
+        <v>112620025</v>
       </c>
       <c r="B71" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8210,34 +7989,38 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>rönningsåsen s., Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>409571</v>
+        <v>409587</v>
       </c>
       <c r="R71" t="n">
-        <v>6941137</v>
+        <v>6941276</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8270,6 +8053,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2023-10-09</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8296,15 +8084,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>112619980</v>
+        <v>112620026</v>
       </c>
       <c r="B72" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8340,10 +8123,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>409502</v>
+        <v>409581</v>
       </c>
       <c r="R72" t="n">
-        <v>6941068</v>
+        <v>6941289</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8407,15 +8190,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>112619978</v>
+        <v>112620027</v>
       </c>
       <c r="B73" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8451,10 +8229,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>409524</v>
+        <v>409602</v>
       </c>
       <c r="R73" t="n">
-        <v>6941094</v>
+        <v>6941388</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8491,7 +8269,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8518,15 +8296,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>112620003</v>
+        <v>112620028</v>
       </c>
       <c r="B74" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8562,10 +8335,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>409522</v>
+        <v>409612</v>
       </c>
       <c r="R74" t="n">
-        <v>6940881</v>
+        <v>6941390</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8602,7 +8375,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8629,15 +8402,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>112619989</v>
+        <v>112620029</v>
       </c>
       <c r="B75" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8673,10 +8441,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>409373</v>
+        <v>409630</v>
       </c>
       <c r="R75" t="n">
-        <v>6941108</v>
+        <v>6941391</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8713,7 +8481,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8740,15 +8508,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>112620012</v>
+        <v>112620030</v>
       </c>
       <c r="B76" t="n">
-        <v>56623</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8784,10 +8547,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>409526</v>
+        <v>409652</v>
       </c>
       <c r="R76" t="n">
-        <v>6940963</v>
+        <v>6941425</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8848,448 +8611,6 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>121648919</v>
-      </c>
-      <c r="B77" t="n">
-        <v>78632</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Rönningsåsen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q77" t="n">
-        <v>409581</v>
-      </c>
-      <c r="R77" t="n">
-        <v>6941403</v>
-      </c>
-      <c r="S77" t="n">
-        <v>10</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>Hede</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AD77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT77" t="inlineStr"/>
-      <c r="AW77" t="inlineStr">
-        <is>
-          <t>Greensway AB</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr">
-        <is>
-          <t>Fastighetsverket NVB 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>121648920</v>
-      </c>
-      <c r="B78" t="n">
-        <v>91678</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>4769</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Svavelriska</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Lactarius scrobiculatus</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Rönningsåsen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q78" t="n">
-        <v>409607</v>
-      </c>
-      <c r="R78" t="n">
-        <v>6941437</v>
-      </c>
-      <c r="S78" t="n">
-        <v>10</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Hede</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AD78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT78" t="inlineStr"/>
-      <c r="AW78" t="inlineStr">
-        <is>
-          <t>Greensway AB</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr">
-        <is>
-          <t>Fastighetsverket NVB 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>121648923</v>
-      </c>
-      <c r="B79" t="n">
-        <v>91091</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>2063</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Grantickeporing</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Skeletocutis chrysella</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Svarthån, Hjd</t>
-        </is>
-      </c>
-      <c r="Q79" t="n">
-        <v>409528</v>
-      </c>
-      <c r="R79" t="n">
-        <v>6940887</v>
-      </c>
-      <c r="S79" t="n">
-        <v>10</v>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>Hede</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AD79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT79" t="inlineStr"/>
-      <c r="AW79" t="inlineStr">
-        <is>
-          <t>Greensway AB</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr">
-        <is>
-          <t>Fastighetsverket NVB 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>121648924</v>
-      </c>
-      <c r="B80" t="n">
-        <v>90763</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Svarthån, Hjd</t>
-        </is>
-      </c>
-      <c r="Q80" t="n">
-        <v>409498</v>
-      </c>
-      <c r="R80" t="n">
-        <v>6940878</v>
-      </c>
-      <c r="S80" t="n">
-        <v>10</v>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Hede</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AD80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT80" t="inlineStr"/>
-      <c r="AW80" t="inlineStr">
-        <is>
-          <t>Greensway AB</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr">
-        <is>
-          <t>Fastighetsverket NVB 2024</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55383-2022 artfynd.xlsx
+++ b/artfynd/A 55383-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AZ76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121648923</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
           <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121648920</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620059</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620060</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
           <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121648919</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1300,6 +1330,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619950</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1406,6 +1441,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619956</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619957</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1618,6 +1663,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619958</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1724,6 +1774,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619959</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1830,6 +1885,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619960</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1936,6 +1996,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619961</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2042,6 +2107,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619962</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2148,6 +2218,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619963</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2254,6 +2329,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619964</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2360,6 +2440,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619965</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2465,6 +2550,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619966</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2571,6 +2661,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619967</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2677,6 +2772,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619968</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2783,6 +2883,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619969</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2889,6 +2994,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619970</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2995,6 +3105,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619972</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3101,6 +3216,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619973</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3207,6 +3327,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619974</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3313,6 +3438,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619976</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3419,6 +3549,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619977</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3525,6 +3660,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619978</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3631,6 +3771,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619979</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3737,6 +3882,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619980</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3843,6 +3993,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619981</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3949,6 +4104,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619982</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4055,6 +4215,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619983</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4161,6 +4326,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619984</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4267,6 +4437,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619985</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4373,6 +4548,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619986</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4479,6 +4659,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619987</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4585,6 +4770,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619988</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4691,6 +4881,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619989</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4797,6 +4992,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619990</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4903,6 +5103,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619991</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5009,6 +5214,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619992</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5115,6 +5325,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619993</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5221,6 +5436,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619994</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5327,6 +5547,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619995</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5433,6 +5658,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619996</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5539,6 +5769,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619997</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5644,6 +5879,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112619998</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5750,6 +5990,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620000</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5856,6 +6101,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620001</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5962,6 +6212,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620002</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6068,6 +6323,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620003</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6174,6 +6434,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620004</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6279,6 +6544,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620005</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6385,6 +6655,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620006</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6491,6 +6766,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620007</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6597,6 +6877,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620008</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6703,6 +6988,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620009</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6809,6 +7099,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620010</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6915,6 +7210,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620011</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7021,6 +7321,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620012</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7127,6 +7432,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620013</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7233,6 +7543,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620015</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7339,6 +7654,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620016</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7445,6 +7765,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620018</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7551,6 +7876,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620019</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7657,6 +7987,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620020</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7763,6 +8098,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620021</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7869,6 +8209,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620022</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7975,6 +8320,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620024</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8081,6 +8431,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620025</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8187,6 +8542,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620026</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8293,6 +8653,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620027</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8399,6 +8764,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620028</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8505,6 +8875,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620029</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8611,8 +8986,90 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112620030</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>